--- a/FM-MN-07_ARGON-01.xlsx
+++ b/FM-MN-07_ARGON-01.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\Maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DFD2CE6-DC8E-4B14-9AA7-75F5C5DDBFBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADA0D42F-1FB1-452B-A39B-1884D500E9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DE5370CA-647C-48FC-A6D6-FC5AAC313DA8}"/>
   </bookViews>
   <sheets>
     <sheet name="ARGON" sheetId="5" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">ARGON!$A$1:$AG$23</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -414,12 +417,21 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -440,15 +452,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1503,80 +1506,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="14" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
-      <c r="Z1" s="25"/>
-      <c r="AA1" s="25"/>
-      <c r="AB1" s="26" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
+      <c r="Y1" s="28"/>
+      <c r="Z1" s="28"/>
+      <c r="AA1" s="28"/>
+      <c r="AB1" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="AC1" s="26"/>
-      <c r="AD1" s="26"/>
-      <c r="AE1" s="26"/>
-      <c r="AF1" s="26"/>
-      <c r="AG1" s="26"/>
+      <c r="AC1" s="29"/>
+      <c r="AD1" s="29"/>
+      <c r="AE1" s="29"/>
+      <c r="AF1" s="29"/>
+      <c r="AG1" s="29"/>
     </row>
     <row r="2" spans="1:33" s="14" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A2" s="25"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="25"/>
-      <c r="V2" s="25"/>
-      <c r="W2" s="25"/>
-      <c r="X2" s="25"/>
-      <c r="Y2" s="25"/>
-      <c r="Z2" s="25"/>
-      <c r="AA2" s="25"/>
-      <c r="AB2" s="26" t="s">
+      <c r="A2" s="28"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
+      <c r="V2" s="28"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="28"/>
+      <c r="Y2" s="28"/>
+      <c r="Z2" s="28"/>
+      <c r="AA2" s="28"/>
+      <c r="AB2" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="AC2" s="26"/>
-      <c r="AD2" s="26"/>
-      <c r="AE2" s="26"/>
-      <c r="AF2" s="26"/>
-      <c r="AG2" s="26"/>
+      <c r="AC2" s="29"/>
+      <c r="AD2" s="29"/>
+      <c r="AE2" s="29"/>
+      <c r="AF2" s="29"/>
+      <c r="AG2" s="29"/>
     </row>
     <row r="3" spans="1:33" s="14" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="17"/>
@@ -1614,49 +1617,49 @@
       <c r="AG3" s="15"/>
     </row>
     <row r="4" spans="1:33" s="10" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="31"/>
-      <c r="M4" s="31"/>
-      <c r="N4" s="31"/>
-      <c r="O4" s="31"/>
-      <c r="P4" s="31"/>
-      <c r="Q4" s="31"/>
-      <c r="R4" s="31"/>
-      <c r="S4" s="31"/>
-      <c r="T4" s="31"/>
-      <c r="U4" s="31"/>
-      <c r="V4" s="31"/>
-      <c r="W4" s="31"/>
-      <c r="X4" s="31"/>
-      <c r="Y4" s="31"/>
-      <c r="Z4" s="31"/>
-      <c r="AA4" s="31"/>
-      <c r="AB4" s="31"/>
-      <c r="AC4" s="31"/>
-      <c r="AD4" s="31"/>
-      <c r="AE4" s="31"/>
-      <c r="AF4" s="31"/>
-      <c r="AG4" s="31"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="34"/>
+      <c r="P4" s="34"/>
+      <c r="Q4" s="34"/>
+      <c r="R4" s="34"/>
+      <c r="S4" s="34"/>
+      <c r="T4" s="34"/>
+      <c r="U4" s="34"/>
+      <c r="V4" s="34"/>
+      <c r="W4" s="34"/>
+      <c r="X4" s="34"/>
+      <c r="Y4" s="34"/>
+      <c r="Z4" s="34"/>
+      <c r="AA4" s="34"/>
+      <c r="AB4" s="34"/>
+      <c r="AC4" s="34"/>
+      <c r="AD4" s="34"/>
+      <c r="AE4" s="34"/>
+      <c r="AF4" s="34"/>
+      <c r="AG4" s="34"/>
     </row>
     <row r="5" spans="1:33" s="10" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A5" s="28"/>
-      <c r="B5" s="30"/>
+      <c r="A5" s="31"/>
+      <c r="B5" s="33"/>
       <c r="C5" s="11">
         <v>1</v>
       </c>
@@ -2066,166 +2069,166 @@
     <row r="14" spans="1:33" ht="22.5" customHeight="1">
       <c r="A14" s="7"/>
       <c r="B14" s="6"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
-      <c r="T14" s="23"/>
-      <c r="U14" s="23"/>
-      <c r="V14" s="23"/>
-      <c r="W14" s="23"/>
-      <c r="X14" s="23"/>
-      <c r="Y14" s="23"/>
-      <c r="Z14" s="23"/>
-      <c r="AA14" s="23"/>
-      <c r="AB14" s="23"/>
-      <c r="AC14" s="23"/>
-      <c r="AD14" s="23"/>
-      <c r="AE14" s="23"/>
-      <c r="AF14" s="23"/>
-      <c r="AG14" s="23"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="27"/>
+      <c r="O14" s="27"/>
+      <c r="P14" s="27"/>
+      <c r="Q14" s="27"/>
+      <c r="R14" s="27"/>
+      <c r="S14" s="27"/>
+      <c r="T14" s="27"/>
+      <c r="U14" s="27"/>
+      <c r="V14" s="27"/>
+      <c r="W14" s="27"/>
+      <c r="X14" s="27"/>
+      <c r="Y14" s="27"/>
+      <c r="Z14" s="27"/>
+      <c r="AA14" s="27"/>
+      <c r="AB14" s="27"/>
+      <c r="AC14" s="27"/>
+      <c r="AD14" s="27"/>
+      <c r="AE14" s="27"/>
+      <c r="AF14" s="27"/>
+      <c r="AG14" s="27"/>
     </row>
     <row r="15" spans="1:33" ht="22.5" customHeight="1">
       <c r="B15" s="5"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="24"/>
-      <c r="N15" s="24"/>
-      <c r="O15" s="24"/>
-      <c r="P15" s="24"/>
-      <c r="Q15" s="24"/>
-      <c r="R15" s="24"/>
-      <c r="S15" s="24"/>
-      <c r="T15" s="24"/>
-      <c r="U15" s="24"/>
-      <c r="V15" s="24"/>
-      <c r="W15" s="24"/>
-      <c r="X15" s="24"/>
-      <c r="Y15" s="24"/>
-      <c r="Z15" s="24"/>
-      <c r="AA15" s="24"/>
-      <c r="AB15" s="24"/>
-      <c r="AC15" s="24"/>
-      <c r="AD15" s="24"/>
-      <c r="AE15" s="24"/>
-      <c r="AF15" s="24"/>
-      <c r="AG15" s="24"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="25"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
+      <c r="M15" s="25"/>
+      <c r="N15" s="25"/>
+      <c r="O15" s="25"/>
+      <c r="P15" s="25"/>
+      <c r="Q15" s="25"/>
+      <c r="R15" s="25"/>
+      <c r="S15" s="25"/>
+      <c r="T15" s="25"/>
+      <c r="U15" s="25"/>
+      <c r="V15" s="25"/>
+      <c r="W15" s="25"/>
+      <c r="X15" s="25"/>
+      <c r="Y15" s="25"/>
+      <c r="Z15" s="25"/>
+      <c r="AA15" s="25"/>
+      <c r="AB15" s="25"/>
+      <c r="AC15" s="25"/>
+      <c r="AD15" s="25"/>
+      <c r="AE15" s="25"/>
+      <c r="AF15" s="25"/>
+      <c r="AG15" s="25"/>
     </row>
     <row r="16" spans="1:33" ht="22.5" customHeight="1">
       <c r="B16" s="5"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
-      <c r="K16" s="32"/>
-      <c r="L16" s="32"/>
-      <c r="M16" s="32"/>
-      <c r="N16" s="32"/>
-      <c r="O16" s="32"/>
-      <c r="P16" s="32"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="32"/>
-      <c r="S16" s="32"/>
-      <c r="T16" s="32"/>
-      <c r="U16" s="32"/>
-      <c r="V16" s="32"/>
-      <c r="W16" s="32"/>
-      <c r="X16" s="32"/>
-      <c r="Y16" s="32"/>
-      <c r="Z16" s="32"/>
-      <c r="AA16" s="32"/>
-      <c r="AB16" s="32"/>
-      <c r="AC16" s="32"/>
-      <c r="AD16" s="32"/>
-      <c r="AE16" s="32"/>
-      <c r="AF16" s="32"/>
-      <c r="AG16" s="32"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="24"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24"/>
+      <c r="R16" s="24"/>
+      <c r="S16" s="24"/>
+      <c r="T16" s="24"/>
+      <c r="U16" s="24"/>
+      <c r="V16" s="24"/>
+      <c r="W16" s="24"/>
+      <c r="X16" s="24"/>
+      <c r="Y16" s="24"/>
+      <c r="Z16" s="24"/>
+      <c r="AA16" s="24"/>
+      <c r="AB16" s="24"/>
+      <c r="AC16" s="24"/>
+      <c r="AD16" s="24"/>
+      <c r="AE16" s="24"/>
+      <c r="AF16" s="24"/>
+      <c r="AG16" s="24"/>
     </row>
     <row r="17" spans="2:33" ht="22.5" customHeight="1">
       <c r="B17" s="5"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="24"/>
-      <c r="M17" s="24"/>
-      <c r="N17" s="24"/>
-      <c r="O17" s="24"/>
-      <c r="P17" s="24"/>
-      <c r="Q17" s="24"/>
-      <c r="R17" s="24"/>
-      <c r="S17" s="24"/>
-      <c r="T17" s="24"/>
-      <c r="U17" s="24"/>
-      <c r="V17" s="24"/>
-      <c r="W17" s="24"/>
-      <c r="X17" s="24"/>
-      <c r="Y17" s="24"/>
-      <c r="Z17" s="24"/>
-      <c r="AA17" s="24"/>
-      <c r="AB17" s="24"/>
-      <c r="AC17" s="24"/>
-      <c r="AD17" s="24"/>
-      <c r="AE17" s="24"/>
-      <c r="AF17" s="24"/>
-      <c r="AG17" s="24"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
+      <c r="M17" s="25"/>
+      <c r="N17" s="25"/>
+      <c r="O17" s="25"/>
+      <c r="P17" s="25"/>
+      <c r="Q17" s="25"/>
+      <c r="R17" s="25"/>
+      <c r="S17" s="25"/>
+      <c r="T17" s="25"/>
+      <c r="U17" s="25"/>
+      <c r="V17" s="25"/>
+      <c r="W17" s="25"/>
+      <c r="X17" s="25"/>
+      <c r="Y17" s="25"/>
+      <c r="Z17" s="25"/>
+      <c r="AA17" s="25"/>
+      <c r="AB17" s="25"/>
+      <c r="AC17" s="25"/>
+      <c r="AD17" s="25"/>
+      <c r="AE17" s="25"/>
+      <c r="AF17" s="25"/>
+      <c r="AG17" s="25"/>
     </row>
     <row r="18" spans="2:33" ht="19.5" customHeight="1">
       <c r="B18" s="21" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="2:33" ht="185.25" customHeight="1">
+    <row r="19" spans="2:33" ht="321" customHeight="1">
       <c r="B19" s="22"/>
     </row>
     <row r="20" spans="2:33" ht="23.25" customHeight="1"/>
     <row r="21" spans="2:33" ht="21">
       <c r="AA21" s="4"/>
       <c r="AB21" s="4"/>
-      <c r="AC21" s="34"/>
-      <c r="AD21" s="34"/>
-      <c r="AE21" s="34"/>
-      <c r="AF21" s="34"/>
-      <c r="AG21" s="34"/>
+      <c r="AC21" s="26"/>
+      <c r="AD21" s="26"/>
+      <c r="AE21" s="26"/>
+      <c r="AF21" s="26"/>
+      <c r="AG21" s="26"/>
     </row>
     <row r="22" spans="2:33" ht="29.25" customHeight="1">
-      <c r="AC22" s="33" t="s">
+      <c r="AC22" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="AD22" s="33"/>
-      <c r="AE22" s="33"/>
-      <c r="AF22" s="33"/>
-      <c r="AG22" s="33"/>
+      <c r="AD22" s="23"/>
+      <c r="AE22" s="23"/>
+      <c r="AF22" s="23"/>
+      <c r="AG22" s="23"/>
     </row>
     <row r="23" spans="2:33" ht="14.25" customHeight="1">
       <c r="C23" s="3"/>
@@ -2235,31 +2238,34 @@
     </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="AC22:AG22"/>
-    <mergeCell ref="AC16:AC17"/>
-    <mergeCell ref="AC21:AG21"/>
-    <mergeCell ref="U16:U17"/>
-    <mergeCell ref="V16:V17"/>
-    <mergeCell ref="X16:X17"/>
-    <mergeCell ref="Y16:Y17"/>
-    <mergeCell ref="Z16:Z17"/>
-    <mergeCell ref="AA16:AA17"/>
-    <mergeCell ref="AB16:AB17"/>
-    <mergeCell ref="AD16:AD17"/>
-    <mergeCell ref="AE16:AE17"/>
-    <mergeCell ref="AF16:AF17"/>
-    <mergeCell ref="AG16:AG17"/>
-    <mergeCell ref="AC14:AC15"/>
-    <mergeCell ref="AD14:AD15"/>
-    <mergeCell ref="AE14:AE15"/>
-    <mergeCell ref="AF14:AF15"/>
-    <mergeCell ref="W16:W17"/>
-    <mergeCell ref="AB14:AB15"/>
-    <mergeCell ref="L16:L17"/>
-    <mergeCell ref="M16:M17"/>
-    <mergeCell ref="N16:N17"/>
-    <mergeCell ref="O16:O17"/>
-    <mergeCell ref="P16:P17"/>
+    <mergeCell ref="AG14:AG15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="A1:AA2"/>
+    <mergeCell ref="AB1:AG1"/>
+    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:AG4"/>
+    <mergeCell ref="T14:T15"/>
+    <mergeCell ref="U14:U15"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="O14:O15"/>
+    <mergeCell ref="P14:P15"/>
+    <mergeCell ref="Q14:Q15"/>
+    <mergeCell ref="R14:R15"/>
+    <mergeCell ref="S14:S15"/>
     <mergeCell ref="H16:H17"/>
     <mergeCell ref="I16:I17"/>
     <mergeCell ref="J16:J17"/>
@@ -2276,39 +2282,36 @@
     <mergeCell ref="N14:N15"/>
     <mergeCell ref="H14:H15"/>
     <mergeCell ref="I14:I15"/>
+    <mergeCell ref="L16:L17"/>
+    <mergeCell ref="M16:M17"/>
+    <mergeCell ref="N16:N17"/>
+    <mergeCell ref="O16:O17"/>
+    <mergeCell ref="P16:P17"/>
+    <mergeCell ref="AC14:AC15"/>
+    <mergeCell ref="AD14:AD15"/>
+    <mergeCell ref="AE14:AE15"/>
+    <mergeCell ref="AF14:AF15"/>
+    <mergeCell ref="W16:W17"/>
+    <mergeCell ref="AB14:AB15"/>
     <mergeCell ref="Z14:Z15"/>
-    <mergeCell ref="O14:O15"/>
-    <mergeCell ref="P14:P15"/>
-    <mergeCell ref="Q14:Q15"/>
-    <mergeCell ref="R14:R15"/>
-    <mergeCell ref="S14:S15"/>
-    <mergeCell ref="T14:T15"/>
-    <mergeCell ref="U14:U15"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="A1:AA2"/>
-    <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="AB2:AG2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:AG4"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="AG14:AG15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="AC22:AG22"/>
+    <mergeCell ref="AC16:AC17"/>
+    <mergeCell ref="AC21:AG21"/>
+    <mergeCell ref="U16:U17"/>
+    <mergeCell ref="V16:V17"/>
+    <mergeCell ref="X16:X17"/>
+    <mergeCell ref="Y16:Y17"/>
+    <mergeCell ref="Z16:Z17"/>
+    <mergeCell ref="AA16:AA17"/>
+    <mergeCell ref="AB16:AB17"/>
+    <mergeCell ref="AD16:AD17"/>
+    <mergeCell ref="AE16:AE17"/>
+    <mergeCell ref="AF16:AF17"/>
+    <mergeCell ref="AG16:AG17"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="85" orientation="landscape" horizontalDpi="4294967292" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="72" orientation="landscape" horizontalDpi="4294967292" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/FM-MN-07_ARGON-01.xlsx
+++ b/FM-MN-07_ARGON-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\Maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADA0D42F-1FB1-452B-A39B-1884D500E9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67790F51-F5D3-4932-A59D-8E7E47CFF2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DE5370CA-647C-48FC-A6D6-FC5AAC313DA8}"/>
   </bookViews>
@@ -69,9 +69,6 @@
     <t>ARGON NO.  ……………...….......……..</t>
   </si>
   <si>
-    <t>ใบตรวจสอบเครื่อง ARGON</t>
-  </si>
-  <si>
     <t xml:space="preserve">เช็ค  BREAKER  เพื่อเช็คระบบไฟฟ้า ตามตำแหน่งไฟ โชว์  และ SWITCH  ต่าง ๆ </t>
   </si>
   <si>
@@ -79,6 +76,9 @@
   </si>
   <si>
     <t>ตรวจสภาความพร้อมของสายไฟฟ้าสายก๊าช  ARGON และชุดหัวเชื่อม</t>
+  </si>
+  <si>
+    <t>ใบตรวจสอบเครื่อง ARGON No.1</t>
   </si>
 </sst>
 </file>
@@ -417,41 +417,41 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -518,15 +518,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2457450</xdr:colOff>
+      <xdr:colOff>2822575</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>69850</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>4876800</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>275166</xdr:rowOff>
+      <xdr:colOff>5241925</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>21166</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -550,7 +550,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2771775" y="2886075"/>
+          <a:off x="3140075" y="2959100"/>
           <a:ext cx="2419350" cy="1094316"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1506,80 +1506,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="14" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A1" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="28"/>
-      <c r="AA1" s="28"/>
-      <c r="AB1" s="29" t="s">
+      <c r="A1" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="25"/>
+      <c r="S1" s="25"/>
+      <c r="T1" s="25"/>
+      <c r="U1" s="25"/>
+      <c r="V1" s="25"/>
+      <c r="W1" s="25"/>
+      <c r="X1" s="25"/>
+      <c r="Y1" s="25"/>
+      <c r="Z1" s="25"/>
+      <c r="AA1" s="25"/>
+      <c r="AB1" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="AC1" s="29"/>
-      <c r="AD1" s="29"/>
-      <c r="AE1" s="29"/>
-      <c r="AF1" s="29"/>
-      <c r="AG1" s="29"/>
+      <c r="AC1" s="26"/>
+      <c r="AD1" s="26"/>
+      <c r="AE1" s="26"/>
+      <c r="AF1" s="26"/>
+      <c r="AG1" s="26"/>
     </row>
     <row r="2" spans="1:33" s="14" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
-      <c r="T2" s="28"/>
-      <c r="U2" s="28"/>
-      <c r="V2" s="28"/>
-      <c r="W2" s="28"/>
-      <c r="X2" s="28"/>
-      <c r="Y2" s="28"/>
-      <c r="Z2" s="28"/>
-      <c r="AA2" s="28"/>
-      <c r="AB2" s="29" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
+      <c r="R2" s="25"/>
+      <c r="S2" s="25"/>
+      <c r="T2" s="25"/>
+      <c r="U2" s="25"/>
+      <c r="V2" s="25"/>
+      <c r="W2" s="25"/>
+      <c r="X2" s="25"/>
+      <c r="Y2" s="25"/>
+      <c r="Z2" s="25"/>
+      <c r="AA2" s="25"/>
+      <c r="AB2" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="AC2" s="29"/>
-      <c r="AD2" s="29"/>
-      <c r="AE2" s="29"/>
-      <c r="AF2" s="29"/>
-      <c r="AG2" s="29"/>
+      <c r="AC2" s="26"/>
+      <c r="AD2" s="26"/>
+      <c r="AE2" s="26"/>
+      <c r="AF2" s="26"/>
+      <c r="AG2" s="26"/>
     </row>
     <row r="3" spans="1:33" s="14" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="17"/>
@@ -1617,49 +1617,49 @@
       <c r="AG3" s="15"/>
     </row>
     <row r="4" spans="1:33" s="10" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="34"/>
-      <c r="K4" s="34"/>
-      <c r="L4" s="34"/>
-      <c r="M4" s="34"/>
-      <c r="N4" s="34"/>
-      <c r="O4" s="34"/>
-      <c r="P4" s="34"/>
-      <c r="Q4" s="34"/>
-      <c r="R4" s="34"/>
-      <c r="S4" s="34"/>
-      <c r="T4" s="34"/>
-      <c r="U4" s="34"/>
-      <c r="V4" s="34"/>
-      <c r="W4" s="34"/>
-      <c r="X4" s="34"/>
-      <c r="Y4" s="34"/>
-      <c r="Z4" s="34"/>
-      <c r="AA4" s="34"/>
-      <c r="AB4" s="34"/>
-      <c r="AC4" s="34"/>
-      <c r="AD4" s="34"/>
-      <c r="AE4" s="34"/>
-      <c r="AF4" s="34"/>
-      <c r="AG4" s="34"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="31"/>
+      <c r="S4" s="31"/>
+      <c r="T4" s="31"/>
+      <c r="U4" s="31"/>
+      <c r="V4" s="31"/>
+      <c r="W4" s="31"/>
+      <c r="X4" s="31"/>
+      <c r="Y4" s="31"/>
+      <c r="Z4" s="31"/>
+      <c r="AA4" s="31"/>
+      <c r="AB4" s="31"/>
+      <c r="AC4" s="31"/>
+      <c r="AD4" s="31"/>
+      <c r="AE4" s="31"/>
+      <c r="AF4" s="31"/>
+      <c r="AG4" s="31"/>
     </row>
     <row r="5" spans="1:33" s="10" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A5" s="31"/>
-      <c r="B5" s="33"/>
+      <c r="A5" s="28"/>
+      <c r="B5" s="30"/>
       <c r="C5" s="11">
         <v>1</v>
       </c>
@@ -1798,7 +1798,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" s="13"/>
       <c r="D7" s="13"/>
@@ -1837,7 +1837,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
@@ -1954,7 +1954,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
@@ -2069,139 +2069,139 @@
     <row r="14" spans="1:33" ht="22.5" customHeight="1">
       <c r="A14" s="7"/>
       <c r="B14" s="6"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="27"/>
-      <c r="L14" s="27"/>
-      <c r="M14" s="27"/>
-      <c r="N14" s="27"/>
-      <c r="O14" s="27"/>
-      <c r="P14" s="27"/>
-      <c r="Q14" s="27"/>
-      <c r="R14" s="27"/>
-      <c r="S14" s="27"/>
-      <c r="T14" s="27"/>
-      <c r="U14" s="27"/>
-      <c r="V14" s="27"/>
-      <c r="W14" s="27"/>
-      <c r="X14" s="27"/>
-      <c r="Y14" s="27"/>
-      <c r="Z14" s="27"/>
-      <c r="AA14" s="27"/>
-      <c r="AB14" s="27"/>
-      <c r="AC14" s="27"/>
-      <c r="AD14" s="27"/>
-      <c r="AE14" s="27"/>
-      <c r="AF14" s="27"/>
-      <c r="AG14" s="27"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
+      <c r="S14" s="23"/>
+      <c r="T14" s="23"/>
+      <c r="U14" s="23"/>
+      <c r="V14" s="23"/>
+      <c r="W14" s="23"/>
+      <c r="X14" s="23"/>
+      <c r="Y14" s="23"/>
+      <c r="Z14" s="23"/>
+      <c r="AA14" s="23"/>
+      <c r="AB14" s="23"/>
+      <c r="AC14" s="23"/>
+      <c r="AD14" s="23"/>
+      <c r="AE14" s="23"/>
+      <c r="AF14" s="23"/>
+      <c r="AG14" s="23"/>
     </row>
     <row r="15" spans="1:33" ht="22.5" customHeight="1">
       <c r="B15" s="5"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="25"/>
-      <c r="L15" s="25"/>
-      <c r="M15" s="25"/>
-      <c r="N15" s="25"/>
-      <c r="O15" s="25"/>
-      <c r="P15" s="25"/>
-      <c r="Q15" s="25"/>
-      <c r="R15" s="25"/>
-      <c r="S15" s="25"/>
-      <c r="T15" s="25"/>
-      <c r="U15" s="25"/>
-      <c r="V15" s="25"/>
-      <c r="W15" s="25"/>
-      <c r="X15" s="25"/>
-      <c r="Y15" s="25"/>
-      <c r="Z15" s="25"/>
-      <c r="AA15" s="25"/>
-      <c r="AB15" s="25"/>
-      <c r="AC15" s="25"/>
-      <c r="AD15" s="25"/>
-      <c r="AE15" s="25"/>
-      <c r="AF15" s="25"/>
-      <c r="AG15" s="25"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="24"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="24"/>
+      <c r="O15" s="24"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="24"/>
+      <c r="R15" s="24"/>
+      <c r="S15" s="24"/>
+      <c r="T15" s="24"/>
+      <c r="U15" s="24"/>
+      <c r="V15" s="24"/>
+      <c r="W15" s="24"/>
+      <c r="X15" s="24"/>
+      <c r="Y15" s="24"/>
+      <c r="Z15" s="24"/>
+      <c r="AA15" s="24"/>
+      <c r="AB15" s="24"/>
+      <c r="AC15" s="24"/>
+      <c r="AD15" s="24"/>
+      <c r="AE15" s="24"/>
+      <c r="AF15" s="24"/>
+      <c r="AG15" s="24"/>
     </row>
     <row r="16" spans="1:33" ht="22.5" customHeight="1">
       <c r="B16" s="5"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="24"/>
-      <c r="O16" s="24"/>
-      <c r="P16" s="24"/>
-      <c r="Q16" s="24"/>
-      <c r="R16" s="24"/>
-      <c r="S16" s="24"/>
-      <c r="T16" s="24"/>
-      <c r="U16" s="24"/>
-      <c r="V16" s="24"/>
-      <c r="W16" s="24"/>
-      <c r="X16" s="24"/>
-      <c r="Y16" s="24"/>
-      <c r="Z16" s="24"/>
-      <c r="AA16" s="24"/>
-      <c r="AB16" s="24"/>
-      <c r="AC16" s="24"/>
-      <c r="AD16" s="24"/>
-      <c r="AE16" s="24"/>
-      <c r="AF16" s="24"/>
-      <c r="AG16" s="24"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="32"/>
+      <c r="L16" s="32"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="32"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="32"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="32"/>
+      <c r="S16" s="32"/>
+      <c r="T16" s="32"/>
+      <c r="U16" s="32"/>
+      <c r="V16" s="32"/>
+      <c r="W16" s="32"/>
+      <c r="X16" s="32"/>
+      <c r="Y16" s="32"/>
+      <c r="Z16" s="32"/>
+      <c r="AA16" s="32"/>
+      <c r="AB16" s="32"/>
+      <c r="AC16" s="32"/>
+      <c r="AD16" s="32"/>
+      <c r="AE16" s="32"/>
+      <c r="AF16" s="32"/>
+      <c r="AG16" s="32"/>
     </row>
     <row r="17" spans="2:33" ht="22.5" customHeight="1">
       <c r="B17" s="5"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="25"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="25"/>
-      <c r="N17" s="25"/>
-      <c r="O17" s="25"/>
-      <c r="P17" s="25"/>
-      <c r="Q17" s="25"/>
-      <c r="R17" s="25"/>
-      <c r="S17" s="25"/>
-      <c r="T17" s="25"/>
-      <c r="U17" s="25"/>
-      <c r="V17" s="25"/>
-      <c r="W17" s="25"/>
-      <c r="X17" s="25"/>
-      <c r="Y17" s="25"/>
-      <c r="Z17" s="25"/>
-      <c r="AA17" s="25"/>
-      <c r="AB17" s="25"/>
-      <c r="AC17" s="25"/>
-      <c r="AD17" s="25"/>
-      <c r="AE17" s="25"/>
-      <c r="AF17" s="25"/>
-      <c r="AG17" s="25"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="24"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24"/>
+      <c r="R17" s="24"/>
+      <c r="S17" s="24"/>
+      <c r="T17" s="24"/>
+      <c r="U17" s="24"/>
+      <c r="V17" s="24"/>
+      <c r="W17" s="24"/>
+      <c r="X17" s="24"/>
+      <c r="Y17" s="24"/>
+      <c r="Z17" s="24"/>
+      <c r="AA17" s="24"/>
+      <c r="AB17" s="24"/>
+      <c r="AC17" s="24"/>
+      <c r="AD17" s="24"/>
+      <c r="AE17" s="24"/>
+      <c r="AF17" s="24"/>
+      <c r="AG17" s="24"/>
     </row>
     <row r="18" spans="2:33" ht="19.5" customHeight="1">
       <c r="B18" s="21" t="s">
@@ -2215,20 +2215,20 @@
     <row r="21" spans="2:33" ht="21">
       <c r="AA21" s="4"/>
       <c r="AB21" s="4"/>
-      <c r="AC21" s="26"/>
-      <c r="AD21" s="26"/>
-      <c r="AE21" s="26"/>
-      <c r="AF21" s="26"/>
-      <c r="AG21" s="26"/>
+      <c r="AC21" s="34"/>
+      <c r="AD21" s="34"/>
+      <c r="AE21" s="34"/>
+      <c r="AF21" s="34"/>
+      <c r="AG21" s="34"/>
     </row>
     <row r="22" spans="2:33" ht="29.25" customHeight="1">
-      <c r="AC22" s="23" t="s">
+      <c r="AC22" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="AD22" s="23"/>
-      <c r="AE22" s="23"/>
-      <c r="AF22" s="23"/>
-      <c r="AG22" s="23"/>
+      <c r="AD22" s="33"/>
+      <c r="AE22" s="33"/>
+      <c r="AF22" s="33"/>
+      <c r="AG22" s="33"/>
     </row>
     <row r="23" spans="2:33" ht="14.25" customHeight="1">
       <c r="C23" s="3"/>
@@ -2238,62 +2238,6 @@
     </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="AG14:AG15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="A1:AA2"/>
-    <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="AB2:AG2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:AG4"/>
-    <mergeCell ref="T14:T15"/>
-    <mergeCell ref="U14:U15"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="O14:O15"/>
-    <mergeCell ref="P14:P15"/>
-    <mergeCell ref="Q14:Q15"/>
-    <mergeCell ref="R14:R15"/>
-    <mergeCell ref="S14:S15"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="AA14:AA15"/>
-    <mergeCell ref="Q16:Q17"/>
-    <mergeCell ref="R16:R17"/>
-    <mergeCell ref="S16:S17"/>
-    <mergeCell ref="T16:T17"/>
-    <mergeCell ref="V14:V15"/>
-    <mergeCell ref="W14:W15"/>
-    <mergeCell ref="X14:X15"/>
-    <mergeCell ref="Y14:Y15"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="L16:L17"/>
-    <mergeCell ref="M16:M17"/>
-    <mergeCell ref="N16:N17"/>
-    <mergeCell ref="O16:O17"/>
-    <mergeCell ref="P16:P17"/>
-    <mergeCell ref="AC14:AC15"/>
-    <mergeCell ref="AD14:AD15"/>
-    <mergeCell ref="AE14:AE15"/>
-    <mergeCell ref="AF14:AF15"/>
-    <mergeCell ref="W16:W17"/>
-    <mergeCell ref="AB14:AB15"/>
-    <mergeCell ref="Z14:Z15"/>
     <mergeCell ref="AC22:AG22"/>
     <mergeCell ref="AC16:AC17"/>
     <mergeCell ref="AC21:AG21"/>
@@ -2308,6 +2252,62 @@
     <mergeCell ref="AE16:AE17"/>
     <mergeCell ref="AF16:AF17"/>
     <mergeCell ref="AG16:AG17"/>
+    <mergeCell ref="AC14:AC15"/>
+    <mergeCell ref="AD14:AD15"/>
+    <mergeCell ref="AE14:AE15"/>
+    <mergeCell ref="AF14:AF15"/>
+    <mergeCell ref="W16:W17"/>
+    <mergeCell ref="AB14:AB15"/>
+    <mergeCell ref="Z14:Z15"/>
+    <mergeCell ref="AA14:AA15"/>
+    <mergeCell ref="Q16:Q17"/>
+    <mergeCell ref="R16:R17"/>
+    <mergeCell ref="S16:S17"/>
+    <mergeCell ref="T16:T17"/>
+    <mergeCell ref="V14:V15"/>
+    <mergeCell ref="W14:W15"/>
+    <mergeCell ref="X14:X15"/>
+    <mergeCell ref="Y14:Y15"/>
+    <mergeCell ref="R14:R15"/>
+    <mergeCell ref="S14:S15"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="L16:L17"/>
+    <mergeCell ref="M16:M17"/>
+    <mergeCell ref="N16:N17"/>
+    <mergeCell ref="O16:O17"/>
+    <mergeCell ref="P16:P17"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="O14:O15"/>
+    <mergeCell ref="P14:P15"/>
+    <mergeCell ref="Q14:Q15"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="AG14:AG15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="A1:AA2"/>
+    <mergeCell ref="AB1:AG1"/>
+    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:AG4"/>
+    <mergeCell ref="T14:T15"/>
+    <mergeCell ref="U14:U15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>

--- a/FM-MN-07_ARGON-01.xlsx
+++ b/FM-MN-07_ARGON-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\Maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67790F51-F5D3-4932-A59D-8E7E47CFF2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D11D46B6-9E49-48C9-9CAA-E75CC098BB4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DE5370CA-647C-48FC-A6D6-FC5AAC313DA8}"/>
   </bookViews>
@@ -414,15 +414,21 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -444,14 +450,8 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1506,80 +1506,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="14" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
-      <c r="Z1" s="25"/>
-      <c r="AA1" s="25"/>
-      <c r="AB1" s="26" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="27"/>
+      <c r="U1" s="27"/>
+      <c r="V1" s="27"/>
+      <c r="W1" s="27"/>
+      <c r="X1" s="27"/>
+      <c r="Y1" s="27"/>
+      <c r="Z1" s="27"/>
+      <c r="AA1" s="27"/>
+      <c r="AB1" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="AC1" s="26"/>
-      <c r="AD1" s="26"/>
-      <c r="AE1" s="26"/>
-      <c r="AF1" s="26"/>
-      <c r="AG1" s="26"/>
+      <c r="AC1" s="28"/>
+      <c r="AD1" s="28"/>
+      <c r="AE1" s="28"/>
+      <c r="AF1" s="28"/>
+      <c r="AG1" s="28"/>
     </row>
     <row r="2" spans="1:33" s="14" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A2" s="25"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="25"/>
-      <c r="V2" s="25"/>
-      <c r="W2" s="25"/>
-      <c r="X2" s="25"/>
-      <c r="Y2" s="25"/>
-      <c r="Z2" s="25"/>
-      <c r="AA2" s="25"/>
-      <c r="AB2" s="26" t="s">
+      <c r="A2" s="27"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
+      <c r="V2" s="27"/>
+      <c r="W2" s="27"/>
+      <c r="X2" s="27"/>
+      <c r="Y2" s="27"/>
+      <c r="Z2" s="27"/>
+      <c r="AA2" s="27"/>
+      <c r="AB2" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="AC2" s="26"/>
-      <c r="AD2" s="26"/>
-      <c r="AE2" s="26"/>
-      <c r="AF2" s="26"/>
-      <c r="AG2" s="26"/>
+      <c r="AC2" s="28"/>
+      <c r="AD2" s="28"/>
+      <c r="AE2" s="28"/>
+      <c r="AF2" s="28"/>
+      <c r="AG2" s="28"/>
     </row>
     <row r="3" spans="1:33" s="14" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="17"/>
@@ -1617,49 +1617,49 @@
       <c r="AG3" s="15"/>
     </row>
     <row r="4" spans="1:33" s="10" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="31"/>
-      <c r="M4" s="31"/>
-      <c r="N4" s="31"/>
-      <c r="O4" s="31"/>
-      <c r="P4" s="31"/>
-      <c r="Q4" s="31"/>
-      <c r="R4" s="31"/>
-      <c r="S4" s="31"/>
-      <c r="T4" s="31"/>
-      <c r="U4" s="31"/>
-      <c r="V4" s="31"/>
-      <c r="W4" s="31"/>
-      <c r="X4" s="31"/>
-      <c r="Y4" s="31"/>
-      <c r="Z4" s="31"/>
-      <c r="AA4" s="31"/>
-      <c r="AB4" s="31"/>
-      <c r="AC4" s="31"/>
-      <c r="AD4" s="31"/>
-      <c r="AE4" s="31"/>
-      <c r="AF4" s="31"/>
-      <c r="AG4" s="31"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="33"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="33"/>
+      <c r="O4" s="33"/>
+      <c r="P4" s="33"/>
+      <c r="Q4" s="33"/>
+      <c r="R4" s="33"/>
+      <c r="S4" s="33"/>
+      <c r="T4" s="33"/>
+      <c r="U4" s="33"/>
+      <c r="V4" s="33"/>
+      <c r="W4" s="33"/>
+      <c r="X4" s="33"/>
+      <c r="Y4" s="33"/>
+      <c r="Z4" s="33"/>
+      <c r="AA4" s="33"/>
+      <c r="AB4" s="33"/>
+      <c r="AC4" s="33"/>
+      <c r="AD4" s="33"/>
+      <c r="AE4" s="33"/>
+      <c r="AF4" s="33"/>
+      <c r="AG4" s="33"/>
     </row>
     <row r="5" spans="1:33" s="10" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A5" s="28"/>
-      <c r="B5" s="30"/>
+      <c r="A5" s="30"/>
+      <c r="B5" s="32"/>
       <c r="C5" s="11">
         <v>1</v>
       </c>
@@ -2069,37 +2069,37 @@
     <row r="14" spans="1:33" ht="22.5" customHeight="1">
       <c r="A14" s="7"/>
       <c r="B14" s="6"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
-      <c r="T14" s="23"/>
-      <c r="U14" s="23"/>
-      <c r="V14" s="23"/>
-      <c r="W14" s="23"/>
-      <c r="X14" s="23"/>
-      <c r="Y14" s="23"/>
-      <c r="Z14" s="23"/>
-      <c r="AA14" s="23"/>
-      <c r="AB14" s="23"/>
-      <c r="AC14" s="23"/>
-      <c r="AD14" s="23"/>
-      <c r="AE14" s="23"/>
-      <c r="AF14" s="23"/>
-      <c r="AG14" s="23"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="26"/>
+      <c r="O14" s="26"/>
+      <c r="P14" s="26"/>
+      <c r="Q14" s="26"/>
+      <c r="R14" s="26"/>
+      <c r="S14" s="26"/>
+      <c r="T14" s="26"/>
+      <c r="U14" s="26"/>
+      <c r="V14" s="26"/>
+      <c r="W14" s="26"/>
+      <c r="X14" s="26"/>
+      <c r="Y14" s="26"/>
+      <c r="Z14" s="26"/>
+      <c r="AA14" s="26"/>
+      <c r="AB14" s="26"/>
+      <c r="AC14" s="26"/>
+      <c r="AD14" s="26"/>
+      <c r="AE14" s="26"/>
+      <c r="AF14" s="26"/>
+      <c r="AG14" s="26"/>
     </row>
     <row r="15" spans="1:33" ht="22.5" customHeight="1">
       <c r="B15" s="5"/>
@@ -2137,37 +2137,37 @@
     </row>
     <row r="16" spans="1:33" ht="22.5" customHeight="1">
       <c r="B16" s="5"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
-      <c r="K16" s="32"/>
-      <c r="L16" s="32"/>
-      <c r="M16" s="32"/>
-      <c r="N16" s="32"/>
-      <c r="O16" s="32"/>
-      <c r="P16" s="32"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="32"/>
-      <c r="S16" s="32"/>
-      <c r="T16" s="32"/>
-      <c r="U16" s="32"/>
-      <c r="V16" s="32"/>
-      <c r="W16" s="32"/>
-      <c r="X16" s="32"/>
-      <c r="Y16" s="32"/>
-      <c r="Z16" s="32"/>
-      <c r="AA16" s="32"/>
-      <c r="AB16" s="32"/>
-      <c r="AC16" s="32"/>
-      <c r="AD16" s="32"/>
-      <c r="AE16" s="32"/>
-      <c r="AF16" s="32"/>
-      <c r="AG16" s="32"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
+      <c r="S16" s="23"/>
+      <c r="T16" s="23"/>
+      <c r="U16" s="23"/>
+      <c r="V16" s="23"/>
+      <c r="W16" s="23"/>
+      <c r="X16" s="23"/>
+      <c r="Y16" s="23"/>
+      <c r="Z16" s="23"/>
+      <c r="AA16" s="23"/>
+      <c r="AB16" s="23"/>
+      <c r="AC16" s="23"/>
+      <c r="AD16" s="23"/>
+      <c r="AE16" s="23"/>
+      <c r="AF16" s="23"/>
+      <c r="AG16" s="23"/>
     </row>
     <row r="17" spans="2:33" ht="22.5" customHeight="1">
       <c r="B17" s="5"/>
@@ -2209,26 +2209,57 @@
       </c>
     </row>
     <row r="19" spans="2:33" ht="321" customHeight="1">
-      <c r="B19" s="22"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="34"/>
+      <c r="K19" s="34"/>
+      <c r="L19" s="34"/>
+      <c r="M19" s="34"/>
+      <c r="N19" s="34"/>
+      <c r="O19" s="34"/>
+      <c r="P19" s="34"/>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
+      <c r="S19" s="34"/>
+      <c r="T19" s="34"/>
+      <c r="U19" s="34"/>
+      <c r="V19" s="34"/>
+      <c r="W19" s="34"/>
+      <c r="X19" s="34"/>
+      <c r="Y19" s="34"/>
+      <c r="Z19" s="34"/>
+      <c r="AA19" s="34"/>
+      <c r="AB19" s="34"/>
+      <c r="AC19" s="34"/>
+      <c r="AD19" s="34"/>
+      <c r="AE19" s="34"/>
+      <c r="AF19" s="34"/>
+      <c r="AG19" s="34"/>
     </row>
     <row r="20" spans="2:33" ht="23.25" customHeight="1"/>
     <row r="21" spans="2:33" ht="21">
       <c r="AA21" s="4"/>
       <c r="AB21" s="4"/>
-      <c r="AC21" s="34"/>
-      <c r="AD21" s="34"/>
-      <c r="AE21" s="34"/>
-      <c r="AF21" s="34"/>
-      <c r="AG21" s="34"/>
+      <c r="AC21" s="25"/>
+      <c r="AD21" s="25"/>
+      <c r="AE21" s="25"/>
+      <c r="AF21" s="25"/>
+      <c r="AG21" s="25"/>
     </row>
     <row r="22" spans="2:33" ht="29.25" customHeight="1">
-      <c r="AC22" s="33" t="s">
+      <c r="AC22" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="AD22" s="33"/>
-      <c r="AE22" s="33"/>
-      <c r="AF22" s="33"/>
-      <c r="AG22" s="33"/>
+      <c r="AD22" s="22"/>
+      <c r="AE22" s="22"/>
+      <c r="AF22" s="22"/>
+      <c r="AG22" s="22"/>
     </row>
     <row r="23" spans="2:33" ht="14.25" customHeight="1">
       <c r="C23" s="3"/>
@@ -2237,61 +2268,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="70">
-    <mergeCell ref="AC22:AG22"/>
-    <mergeCell ref="AC16:AC17"/>
-    <mergeCell ref="AC21:AG21"/>
-    <mergeCell ref="U16:U17"/>
-    <mergeCell ref="V16:V17"/>
-    <mergeCell ref="X16:X17"/>
-    <mergeCell ref="Y16:Y17"/>
-    <mergeCell ref="Z16:Z17"/>
-    <mergeCell ref="AA16:AA17"/>
-    <mergeCell ref="AB16:AB17"/>
-    <mergeCell ref="AD16:AD17"/>
-    <mergeCell ref="AE16:AE17"/>
-    <mergeCell ref="AF16:AF17"/>
-    <mergeCell ref="AG16:AG17"/>
-    <mergeCell ref="AC14:AC15"/>
-    <mergeCell ref="AD14:AD15"/>
-    <mergeCell ref="AE14:AE15"/>
-    <mergeCell ref="AF14:AF15"/>
-    <mergeCell ref="W16:W17"/>
-    <mergeCell ref="AB14:AB15"/>
-    <mergeCell ref="Z14:Z15"/>
-    <mergeCell ref="AA14:AA15"/>
-    <mergeCell ref="Q16:Q17"/>
-    <mergeCell ref="R16:R17"/>
-    <mergeCell ref="S16:S17"/>
-    <mergeCell ref="T16:T17"/>
-    <mergeCell ref="V14:V15"/>
-    <mergeCell ref="W14:W15"/>
-    <mergeCell ref="X14:X15"/>
-    <mergeCell ref="Y14:Y15"/>
-    <mergeCell ref="R14:R15"/>
-    <mergeCell ref="S14:S15"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="L16:L17"/>
-    <mergeCell ref="M16:M17"/>
-    <mergeCell ref="N16:N17"/>
-    <mergeCell ref="O16:O17"/>
-    <mergeCell ref="P16:P17"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="O14:O15"/>
-    <mergeCell ref="P14:P15"/>
-    <mergeCell ref="Q14:Q15"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
+  <mergeCells count="71">
     <mergeCell ref="AG14:AG15"/>
     <mergeCell ref="L14:L15"/>
     <mergeCell ref="M14:M15"/>
@@ -2308,6 +2285,61 @@
     <mergeCell ref="C14:C15"/>
     <mergeCell ref="D14:D15"/>
     <mergeCell ref="E14:E15"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="O16:O17"/>
+    <mergeCell ref="P16:P17"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="O14:O15"/>
+    <mergeCell ref="P14:P15"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="L16:L17"/>
+    <mergeCell ref="M16:M17"/>
+    <mergeCell ref="N16:N17"/>
+    <mergeCell ref="Q16:Q17"/>
+    <mergeCell ref="R16:R17"/>
+    <mergeCell ref="S16:S17"/>
+    <mergeCell ref="T16:T17"/>
+    <mergeCell ref="V14:V15"/>
+    <mergeCell ref="R14:R15"/>
+    <mergeCell ref="S14:S15"/>
+    <mergeCell ref="Q14:Q15"/>
+    <mergeCell ref="AC14:AC15"/>
+    <mergeCell ref="AD14:AD15"/>
+    <mergeCell ref="AE14:AE15"/>
+    <mergeCell ref="AF14:AF15"/>
+    <mergeCell ref="W16:W17"/>
+    <mergeCell ref="AB14:AB15"/>
+    <mergeCell ref="Z14:Z15"/>
+    <mergeCell ref="AA14:AA15"/>
+    <mergeCell ref="W14:W15"/>
+    <mergeCell ref="X14:X15"/>
+    <mergeCell ref="Y14:Y15"/>
+    <mergeCell ref="AC22:AG22"/>
+    <mergeCell ref="AC16:AC17"/>
+    <mergeCell ref="AC21:AG21"/>
+    <mergeCell ref="U16:U17"/>
+    <mergeCell ref="V16:V17"/>
+    <mergeCell ref="X16:X17"/>
+    <mergeCell ref="Y16:Y17"/>
+    <mergeCell ref="Z16:Z17"/>
+    <mergeCell ref="AA16:AA17"/>
+    <mergeCell ref="AB16:AB17"/>
+    <mergeCell ref="AD16:AD17"/>
+    <mergeCell ref="AE16:AE17"/>
+    <mergeCell ref="AF16:AF17"/>
+    <mergeCell ref="AG16:AG17"/>
+    <mergeCell ref="B19:AG19"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>

--- a/FM-MN-07_ARGON-01.xlsx
+++ b/FM-MN-07_ARGON-01.xlsx
@@ -347,7 +347,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -452,6 +452,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1790,8 +1793,16 @@
       <c r="AB6" s="29" t="n"/>
       <c r="AC6" s="29" t="n"/>
       <c r="AD6" s="29" t="n"/>
-      <c r="AE6" s="29" t="n"/>
-      <c r="AF6" s="29" t="n"/>
+      <c r="AE6" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF6" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG6" s="29" t="n"/>
     </row>
     <row r="7" ht="15.75" customFormat="1" customHeight="1" s="10">
@@ -1831,8 +1842,16 @@
       <c r="AB7" s="29" t="n"/>
       <c r="AC7" s="29" t="n"/>
       <c r="AD7" s="29" t="n"/>
-      <c r="AE7" s="29" t="n"/>
-      <c r="AF7" s="29" t="n"/>
+      <c r="AE7" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF7" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG7" s="29" t="n"/>
     </row>
     <row r="8" ht="15.75" customFormat="1" customHeight="1" s="10">
@@ -1872,8 +1891,16 @@
       <c r="AB8" s="29" t="n"/>
       <c r="AC8" s="29" t="n"/>
       <c r="AD8" s="29" t="n"/>
-      <c r="AE8" s="29" t="n"/>
-      <c r="AF8" s="29" t="n"/>
+      <c r="AE8" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF8" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG8" s="29" t="n"/>
     </row>
     <row r="9" ht="15.75" customFormat="1" customHeight="1" s="10">
@@ -1913,8 +1940,16 @@
       <c r="AB9" s="29" t="n"/>
       <c r="AC9" s="29" t="n"/>
       <c r="AD9" s="29" t="n"/>
-      <c r="AE9" s="29" t="n"/>
-      <c r="AF9" s="29" t="n"/>
+      <c r="AE9" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF9" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG9" s="29" t="n"/>
     </row>
     <row r="10" ht="15.75" customFormat="1" customHeight="1" s="10">
@@ -1954,8 +1989,16 @@
       <c r="AB10" s="29" t="n"/>
       <c r="AC10" s="29" t="n"/>
       <c r="AD10" s="29" t="n"/>
-      <c r="AE10" s="29" t="n"/>
-      <c r="AF10" s="29" t="n"/>
+      <c r="AE10" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF10" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG10" s="29" t="n"/>
     </row>
     <row r="11" ht="15.75" customFormat="1" customHeight="1" s="10">
@@ -1995,8 +2038,16 @@
       <c r="AB11" s="29" t="n"/>
       <c r="AC11" s="29" t="n"/>
       <c r="AD11" s="29" t="n"/>
-      <c r="AE11" s="29" t="n"/>
-      <c r="AF11" s="29" t="n"/>
+      <c r="AE11" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF11" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG11" s="29" t="n"/>
     </row>
     <row r="12" ht="15.75" customFormat="1" customHeight="1" s="10">
@@ -2036,8 +2087,16 @@
       <c r="AB12" s="29" t="n"/>
       <c r="AC12" s="29" t="n"/>
       <c r="AD12" s="29" t="n"/>
-      <c r="AE12" s="29" t="n"/>
-      <c r="AF12" s="29" t="n"/>
+      <c r="AE12" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF12" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG12" s="29" t="n"/>
     </row>
     <row r="13" ht="15.75" customFormat="1" customHeight="1" s="10">
@@ -2077,8 +2136,16 @@
       <c r="AB13" s="29" t="n"/>
       <c r="AC13" s="29" t="n"/>
       <c r="AD13" s="29" t="n"/>
-      <c r="AE13" s="29" t="n"/>
-      <c r="AF13" s="29" t="n"/>
+      <c r="AE13" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF13" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG13" s="29" t="n"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
@@ -2112,8 +2179,16 @@
       <c r="AB14" s="40" t="n"/>
       <c r="AC14" s="40" t="n"/>
       <c r="AD14" s="40" t="n"/>
-      <c r="AE14" s="40" t="n"/>
-      <c r="AF14" s="40" t="n"/>
+      <c r="AE14" s="42" t="inlineStr">
+        <is>
+          <t>อินทัช เป็นสุข</t>
+        </is>
+      </c>
+      <c r="AF14" s="42" t="inlineStr">
+        <is>
+          <t>อินทัช เป็นสุข</t>
+        </is>
+      </c>
       <c r="AG14" s="40" t="n"/>
     </row>
     <row r="15" ht="22.5" customHeight="1">
@@ -2226,7 +2301,7 @@
       </c>
     </row>
     <row r="19" ht="321" customHeight="1">
-      <c r="B19" s="34" t="n"/>
+      <c r="B19" s="34" t="inlineStr"/>
     </row>
     <row r="20" ht="23.25" customHeight="1"/>
     <row r="21" ht="21" customHeight="1">

--- a/FM-MN-07_ARGON-01.xlsx
+++ b/FM-MN-07_ARGON-01.xlsx
@@ -1765,45 +1765,37 @@
           <t>ตรวจสภาพความพรัอมโดยรวมของเครื่อง</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n"/>
-      <c r="D6" s="29" t="n"/>
-      <c r="E6" s="29" t="n"/>
-      <c r="F6" s="29" t="n"/>
-      <c r="G6" s="29" t="n"/>
-      <c r="H6" s="29" t="n"/>
-      <c r="I6" s="29" t="n"/>
-      <c r="J6" s="29" t="n"/>
-      <c r="K6" s="29" t="n"/>
-      <c r="L6" s="29" t="n"/>
-      <c r="M6" s="29" t="n"/>
-      <c r="N6" s="29" t="n"/>
-      <c r="O6" s="29" t="n"/>
-      <c r="P6" s="29" t="n"/>
-      <c r="Q6" s="29" t="n"/>
-      <c r="R6" s="29" t="n"/>
-      <c r="S6" s="29" t="n"/>
-      <c r="T6" s="29" t="n"/>
-      <c r="U6" s="29" t="n"/>
-      <c r="V6" s="29" t="n"/>
-      <c r="W6" s="29" t="n"/>
-      <c r="X6" s="29" t="n"/>
-      <c r="Y6" s="29" t="n"/>
-      <c r="Z6" s="29" t="n"/>
-      <c r="AA6" s="29" t="n"/>
-      <c r="AB6" s="29" t="n"/>
-      <c r="AC6" s="29" t="n"/>
-      <c r="AD6" s="29" t="n"/>
-      <c r="AE6" s="29" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF6" s="29" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG6" s="29" t="n"/>
+      <c r="C6" s="29" t="inlineStr"/>
+      <c r="D6" s="29" t="inlineStr"/>
+      <c r="E6" s="29" t="inlineStr"/>
+      <c r="F6" s="29" t="inlineStr"/>
+      <c r="G6" s="29" t="inlineStr"/>
+      <c r="H6" s="29" t="inlineStr"/>
+      <c r="I6" s="29" t="inlineStr"/>
+      <c r="J6" s="29" t="inlineStr"/>
+      <c r="K6" s="29" t="inlineStr"/>
+      <c r="L6" s="29" t="inlineStr"/>
+      <c r="M6" s="29" t="inlineStr"/>
+      <c r="N6" s="29" t="inlineStr"/>
+      <c r="O6" s="29" t="inlineStr"/>
+      <c r="P6" s="29" t="inlineStr"/>
+      <c r="Q6" s="29" t="inlineStr"/>
+      <c r="R6" s="29" t="inlineStr"/>
+      <c r="S6" s="29" t="inlineStr"/>
+      <c r="T6" s="29" t="inlineStr"/>
+      <c r="U6" s="29" t="inlineStr"/>
+      <c r="V6" s="29" t="inlineStr"/>
+      <c r="W6" s="29" t="inlineStr"/>
+      <c r="X6" s="29" t="inlineStr"/>
+      <c r="Y6" s="29" t="inlineStr"/>
+      <c r="Z6" s="29" t="inlineStr"/>
+      <c r="AA6" s="29" t="inlineStr"/>
+      <c r="AB6" s="29" t="inlineStr"/>
+      <c r="AC6" s="29" t="inlineStr"/>
+      <c r="AD6" s="29" t="inlineStr"/>
+      <c r="AE6" s="29" t="inlineStr"/>
+      <c r="AF6" s="29" t="inlineStr"/>
+      <c r="AG6" s="29" t="inlineStr"/>
     </row>
     <row r="7" ht="15.75" customFormat="1" customHeight="1" s="10">
       <c r="A7" s="9" t="n">
@@ -1814,45 +1806,37 @@
           <t xml:space="preserve">เช็ค  BREAKER  เพื่อเช็คระบบไฟฟ้า ตามตำแหน่งไฟ โชว์  และ SWITCH  ต่าง ๆ </t>
         </is>
       </c>
-      <c r="C7" s="29" t="n"/>
-      <c r="D7" s="29" t="n"/>
-      <c r="E7" s="29" t="n"/>
-      <c r="F7" s="29" t="n"/>
-      <c r="G7" s="29" t="n"/>
-      <c r="H7" s="29" t="n"/>
-      <c r="I7" s="29" t="n"/>
-      <c r="J7" s="29" t="n"/>
-      <c r="K7" s="29" t="n"/>
-      <c r="L7" s="29" t="n"/>
-      <c r="M7" s="29" t="n"/>
-      <c r="N7" s="29" t="n"/>
-      <c r="O7" s="29" t="n"/>
-      <c r="P7" s="29" t="n"/>
-      <c r="Q7" s="29" t="n"/>
-      <c r="R7" s="29" t="n"/>
-      <c r="S7" s="29" t="n"/>
-      <c r="T7" s="29" t="n"/>
-      <c r="U7" s="29" t="n"/>
-      <c r="V7" s="29" t="n"/>
-      <c r="W7" s="29" t="n"/>
-      <c r="X7" s="29" t="n"/>
-      <c r="Y7" s="29" t="n"/>
-      <c r="Z7" s="29" t="n"/>
-      <c r="AA7" s="29" t="n"/>
-      <c r="AB7" s="29" t="n"/>
-      <c r="AC7" s="29" t="n"/>
-      <c r="AD7" s="29" t="n"/>
-      <c r="AE7" s="29" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF7" s="29" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG7" s="29" t="n"/>
+      <c r="C7" s="29" t="inlineStr"/>
+      <c r="D7" s="29" t="inlineStr"/>
+      <c r="E7" s="29" t="inlineStr"/>
+      <c r="F7" s="29" t="inlineStr"/>
+      <c r="G7" s="29" t="inlineStr"/>
+      <c r="H7" s="29" t="inlineStr"/>
+      <c r="I7" s="29" t="inlineStr"/>
+      <c r="J7" s="29" t="inlineStr"/>
+      <c r="K7" s="29" t="inlineStr"/>
+      <c r="L7" s="29" t="inlineStr"/>
+      <c r="M7" s="29" t="inlineStr"/>
+      <c r="N7" s="29" t="inlineStr"/>
+      <c r="O7" s="29" t="inlineStr"/>
+      <c r="P7" s="29" t="inlineStr"/>
+      <c r="Q7" s="29" t="inlineStr"/>
+      <c r="R7" s="29" t="inlineStr"/>
+      <c r="S7" s="29" t="inlineStr"/>
+      <c r="T7" s="29" t="inlineStr"/>
+      <c r="U7" s="29" t="inlineStr"/>
+      <c r="V7" s="29" t="inlineStr"/>
+      <c r="W7" s="29" t="inlineStr"/>
+      <c r="X7" s="29" t="inlineStr"/>
+      <c r="Y7" s="29" t="inlineStr"/>
+      <c r="Z7" s="29" t="inlineStr"/>
+      <c r="AA7" s="29" t="inlineStr"/>
+      <c r="AB7" s="29" t="inlineStr"/>
+      <c r="AC7" s="29" t="inlineStr"/>
+      <c r="AD7" s="29" t="inlineStr"/>
+      <c r="AE7" s="29" t="inlineStr"/>
+      <c r="AF7" s="29" t="inlineStr"/>
+      <c r="AG7" s="29" t="inlineStr"/>
     </row>
     <row r="8" ht="15.75" customFormat="1" customHeight="1" s="10">
       <c r="A8" s="9" t="n">
@@ -1863,45 +1847,37 @@
           <t>ตรวจสภาพความพร้อมของมาตราวัดแรงดันของมาตรา วัดแรงดันของก๊าช  ARGON  และปรับตั้งอย่างถูกวิธี</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n"/>
-      <c r="D8" s="29" t="n"/>
-      <c r="E8" s="29" t="n"/>
-      <c r="F8" s="29" t="n"/>
-      <c r="G8" s="29" t="n"/>
-      <c r="H8" s="29" t="n"/>
-      <c r="I8" s="29" t="n"/>
-      <c r="J8" s="29" t="n"/>
-      <c r="K8" s="29" t="n"/>
-      <c r="L8" s="29" t="n"/>
-      <c r="M8" s="29" t="n"/>
-      <c r="N8" s="29" t="n"/>
-      <c r="O8" s="29" t="n"/>
-      <c r="P8" s="29" t="n"/>
-      <c r="Q8" s="29" t="n"/>
-      <c r="R8" s="29" t="n"/>
-      <c r="S8" s="29" t="n"/>
-      <c r="T8" s="29" t="n"/>
-      <c r="U8" s="29" t="n"/>
-      <c r="V8" s="29" t="n"/>
-      <c r="W8" s="29" t="n"/>
-      <c r="X8" s="29" t="n"/>
-      <c r="Y8" s="29" t="n"/>
-      <c r="Z8" s="29" t="n"/>
-      <c r="AA8" s="29" t="n"/>
-      <c r="AB8" s="29" t="n"/>
-      <c r="AC8" s="29" t="n"/>
-      <c r="AD8" s="29" t="n"/>
-      <c r="AE8" s="29" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF8" s="29" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG8" s="29" t="n"/>
+      <c r="C8" s="29" t="inlineStr"/>
+      <c r="D8" s="29" t="inlineStr"/>
+      <c r="E8" s="29" t="inlineStr"/>
+      <c r="F8" s="29" t="inlineStr"/>
+      <c r="G8" s="29" t="inlineStr"/>
+      <c r="H8" s="29" t="inlineStr"/>
+      <c r="I8" s="29" t="inlineStr"/>
+      <c r="J8" s="29" t="inlineStr"/>
+      <c r="K8" s="29" t="inlineStr"/>
+      <c r="L8" s="29" t="inlineStr"/>
+      <c r="M8" s="29" t="inlineStr"/>
+      <c r="N8" s="29" t="inlineStr"/>
+      <c r="O8" s="29" t="inlineStr"/>
+      <c r="P8" s="29" t="inlineStr"/>
+      <c r="Q8" s="29" t="inlineStr"/>
+      <c r="R8" s="29" t="inlineStr"/>
+      <c r="S8" s="29" t="inlineStr"/>
+      <c r="T8" s="29" t="inlineStr"/>
+      <c r="U8" s="29" t="inlineStr"/>
+      <c r="V8" s="29" t="inlineStr"/>
+      <c r="W8" s="29" t="inlineStr"/>
+      <c r="X8" s="29" t="inlineStr"/>
+      <c r="Y8" s="29" t="inlineStr"/>
+      <c r="Z8" s="29" t="inlineStr"/>
+      <c r="AA8" s="29" t="inlineStr"/>
+      <c r="AB8" s="29" t="inlineStr"/>
+      <c r="AC8" s="29" t="inlineStr"/>
+      <c r="AD8" s="29" t="inlineStr"/>
+      <c r="AE8" s="29" t="inlineStr"/>
+      <c r="AF8" s="29" t="inlineStr"/>
+      <c r="AG8" s="29" t="inlineStr"/>
     </row>
     <row r="9" ht="15.75" customFormat="1" customHeight="1" s="10">
       <c r="A9" s="9" t="n">
@@ -1912,45 +1888,37 @@
           <t>ตรวจุดต่อของสายก๊าช  ARGON  ก่อนว่ารั่วหรือไม่</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n"/>
-      <c r="D9" s="29" t="n"/>
-      <c r="E9" s="29" t="n"/>
-      <c r="F9" s="29" t="n"/>
-      <c r="G9" s="29" t="n"/>
-      <c r="H9" s="29" t="n"/>
-      <c r="I9" s="29" t="n"/>
-      <c r="J9" s="29" t="n"/>
-      <c r="K9" s="29" t="n"/>
-      <c r="L9" s="29" t="n"/>
-      <c r="M9" s="29" t="n"/>
-      <c r="N9" s="29" t="n"/>
-      <c r="O9" s="29" t="n"/>
-      <c r="P9" s="29" t="n"/>
-      <c r="Q9" s="29" t="n"/>
-      <c r="R9" s="29" t="n"/>
-      <c r="S9" s="29" t="n"/>
-      <c r="T9" s="29" t="n"/>
-      <c r="U9" s="29" t="n"/>
-      <c r="V9" s="29" t="n"/>
-      <c r="W9" s="29" t="n"/>
-      <c r="X9" s="29" t="n"/>
-      <c r="Y9" s="29" t="n"/>
-      <c r="Z9" s="29" t="n"/>
-      <c r="AA9" s="29" t="n"/>
-      <c r="AB9" s="29" t="n"/>
-      <c r="AC9" s="29" t="n"/>
-      <c r="AD9" s="29" t="n"/>
-      <c r="AE9" s="29" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF9" s="29" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG9" s="29" t="n"/>
+      <c r="C9" s="29" t="inlineStr"/>
+      <c r="D9" s="29" t="inlineStr"/>
+      <c r="E9" s="29" t="inlineStr"/>
+      <c r="F9" s="29" t="inlineStr"/>
+      <c r="G9" s="29" t="inlineStr"/>
+      <c r="H9" s="29" t="inlineStr"/>
+      <c r="I9" s="29" t="inlineStr"/>
+      <c r="J9" s="29" t="inlineStr"/>
+      <c r="K9" s="29" t="inlineStr"/>
+      <c r="L9" s="29" t="inlineStr"/>
+      <c r="M9" s="29" t="inlineStr"/>
+      <c r="N9" s="29" t="inlineStr"/>
+      <c r="O9" s="29" t="inlineStr"/>
+      <c r="P9" s="29" t="inlineStr"/>
+      <c r="Q9" s="29" t="inlineStr"/>
+      <c r="R9" s="29" t="inlineStr"/>
+      <c r="S9" s="29" t="inlineStr"/>
+      <c r="T9" s="29" t="inlineStr"/>
+      <c r="U9" s="29" t="inlineStr"/>
+      <c r="V9" s="29" t="inlineStr"/>
+      <c r="W9" s="29" t="inlineStr"/>
+      <c r="X9" s="29" t="inlineStr"/>
+      <c r="Y9" s="29" t="inlineStr"/>
+      <c r="Z9" s="29" t="inlineStr"/>
+      <c r="AA9" s="29" t="inlineStr"/>
+      <c r="AB9" s="29" t="inlineStr"/>
+      <c r="AC9" s="29" t="inlineStr"/>
+      <c r="AD9" s="29" t="inlineStr"/>
+      <c r="AE9" s="29" t="inlineStr"/>
+      <c r="AF9" s="29" t="inlineStr"/>
+      <c r="AG9" s="29" t="inlineStr"/>
     </row>
     <row r="10" ht="15.75" customFormat="1" customHeight="1" s="10">
       <c r="A10" s="9" t="n">
@@ -1961,45 +1929,37 @@
           <t>ตรวจสภาพความพร้อมของสายกราว์</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n"/>
-      <c r="D10" s="29" t="n"/>
-      <c r="E10" s="29" t="n"/>
-      <c r="F10" s="29" t="n"/>
-      <c r="G10" s="29" t="n"/>
-      <c r="H10" s="29" t="n"/>
-      <c r="I10" s="29" t="n"/>
-      <c r="J10" s="29" t="n"/>
-      <c r="K10" s="29" t="n"/>
-      <c r="L10" s="29" t="n"/>
-      <c r="M10" s="29" t="n"/>
-      <c r="N10" s="29" t="n"/>
-      <c r="O10" s="29" t="n"/>
-      <c r="P10" s="29" t="n"/>
-      <c r="Q10" s="29" t="n"/>
-      <c r="R10" s="29" t="n"/>
-      <c r="S10" s="29" t="n"/>
-      <c r="T10" s="29" t="n"/>
-      <c r="U10" s="29" t="n"/>
-      <c r="V10" s="29" t="n"/>
-      <c r="W10" s="29" t="n"/>
-      <c r="X10" s="29" t="n"/>
-      <c r="Y10" s="29" t="n"/>
-      <c r="Z10" s="29" t="n"/>
-      <c r="AA10" s="29" t="n"/>
-      <c r="AB10" s="29" t="n"/>
-      <c r="AC10" s="29" t="n"/>
-      <c r="AD10" s="29" t="n"/>
-      <c r="AE10" s="29" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF10" s="29" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG10" s="29" t="n"/>
+      <c r="C10" s="29" t="inlineStr"/>
+      <c r="D10" s="29" t="inlineStr"/>
+      <c r="E10" s="29" t="inlineStr"/>
+      <c r="F10" s="29" t="inlineStr"/>
+      <c r="G10" s="29" t="inlineStr"/>
+      <c r="H10" s="29" t="inlineStr"/>
+      <c r="I10" s="29" t="inlineStr"/>
+      <c r="J10" s="29" t="inlineStr"/>
+      <c r="K10" s="29" t="inlineStr"/>
+      <c r="L10" s="29" t="inlineStr"/>
+      <c r="M10" s="29" t="inlineStr"/>
+      <c r="N10" s="29" t="inlineStr"/>
+      <c r="O10" s="29" t="inlineStr"/>
+      <c r="P10" s="29" t="inlineStr"/>
+      <c r="Q10" s="29" t="inlineStr"/>
+      <c r="R10" s="29" t="inlineStr"/>
+      <c r="S10" s="29" t="inlineStr"/>
+      <c r="T10" s="29" t="inlineStr"/>
+      <c r="U10" s="29" t="inlineStr"/>
+      <c r="V10" s="29" t="inlineStr"/>
+      <c r="W10" s="29" t="inlineStr"/>
+      <c r="X10" s="29" t="inlineStr"/>
+      <c r="Y10" s="29" t="inlineStr"/>
+      <c r="Z10" s="29" t="inlineStr"/>
+      <c r="AA10" s="29" t="inlineStr"/>
+      <c r="AB10" s="29" t="inlineStr"/>
+      <c r="AC10" s="29" t="inlineStr"/>
+      <c r="AD10" s="29" t="inlineStr"/>
+      <c r="AE10" s="29" t="inlineStr"/>
+      <c r="AF10" s="29" t="inlineStr"/>
+      <c r="AG10" s="29" t="inlineStr"/>
     </row>
     <row r="11" ht="15.75" customFormat="1" customHeight="1" s="10">
       <c r="A11" s="9" t="n">
@@ -2010,45 +1970,37 @@
           <t>ตรวจสภาความพร้อมของสายไฟฟ้าสายก๊าช  ARGON และชุดหัวเชื่อม</t>
         </is>
       </c>
-      <c r="C11" s="29" t="n"/>
-      <c r="D11" s="29" t="n"/>
-      <c r="E11" s="29" t="n"/>
-      <c r="F11" s="29" t="n"/>
-      <c r="G11" s="29" t="n"/>
-      <c r="H11" s="29" t="n"/>
-      <c r="I11" s="29" t="n"/>
-      <c r="J11" s="29" t="n"/>
-      <c r="K11" s="29" t="n"/>
-      <c r="L11" s="29" t="n"/>
-      <c r="M11" s="29" t="n"/>
-      <c r="N11" s="29" t="n"/>
-      <c r="O11" s="29" t="n"/>
-      <c r="P11" s="29" t="n"/>
-      <c r="Q11" s="29" t="n"/>
-      <c r="R11" s="29" t="n"/>
-      <c r="S11" s="29" t="n"/>
-      <c r="T11" s="29" t="n"/>
-      <c r="U11" s="29" t="n"/>
-      <c r="V11" s="29" t="n"/>
-      <c r="W11" s="29" t="n"/>
-      <c r="X11" s="29" t="n"/>
-      <c r="Y11" s="29" t="n"/>
-      <c r="Z11" s="29" t="n"/>
-      <c r="AA11" s="29" t="n"/>
-      <c r="AB11" s="29" t="n"/>
-      <c r="AC11" s="29" t="n"/>
-      <c r="AD11" s="29" t="n"/>
-      <c r="AE11" s="29" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF11" s="29" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG11" s="29" t="n"/>
+      <c r="C11" s="29" t="inlineStr"/>
+      <c r="D11" s="29" t="inlineStr"/>
+      <c r="E11" s="29" t="inlineStr"/>
+      <c r="F11" s="29" t="inlineStr"/>
+      <c r="G11" s="29" t="inlineStr"/>
+      <c r="H11" s="29" t="inlineStr"/>
+      <c r="I11" s="29" t="inlineStr"/>
+      <c r="J11" s="29" t="inlineStr"/>
+      <c r="K11" s="29" t="inlineStr"/>
+      <c r="L11" s="29" t="inlineStr"/>
+      <c r="M11" s="29" t="inlineStr"/>
+      <c r="N11" s="29" t="inlineStr"/>
+      <c r="O11" s="29" t="inlineStr"/>
+      <c r="P11" s="29" t="inlineStr"/>
+      <c r="Q11" s="29" t="inlineStr"/>
+      <c r="R11" s="29" t="inlineStr"/>
+      <c r="S11" s="29" t="inlineStr"/>
+      <c r="T11" s="29" t="inlineStr"/>
+      <c r="U11" s="29" t="inlineStr"/>
+      <c r="V11" s="29" t="inlineStr"/>
+      <c r="W11" s="29" t="inlineStr"/>
+      <c r="X11" s="29" t="inlineStr"/>
+      <c r="Y11" s="29" t="inlineStr"/>
+      <c r="Z11" s="29" t="inlineStr"/>
+      <c r="AA11" s="29" t="inlineStr"/>
+      <c r="AB11" s="29" t="inlineStr"/>
+      <c r="AC11" s="29" t="inlineStr"/>
+      <c r="AD11" s="29" t="inlineStr"/>
+      <c r="AE11" s="29" t="inlineStr"/>
+      <c r="AF11" s="29" t="inlineStr"/>
+      <c r="AG11" s="29" t="inlineStr"/>
     </row>
     <row r="12" ht="15.75" customFormat="1" customHeight="1" s="10">
       <c r="A12" s="9" t="n">
@@ -2059,45 +2011,37 @@
           <t>ตรวจสภาพความพร้อมของ  SWITCH  หัวเชื่อม</t>
         </is>
       </c>
-      <c r="C12" s="29" t="n"/>
-      <c r="D12" s="29" t="n"/>
-      <c r="E12" s="29" t="n"/>
-      <c r="F12" s="29" t="n"/>
-      <c r="G12" s="29" t="n"/>
-      <c r="H12" s="29" t="n"/>
-      <c r="I12" s="29" t="n"/>
-      <c r="J12" s="29" t="n"/>
-      <c r="K12" s="29" t="n"/>
-      <c r="L12" s="29" t="n"/>
-      <c r="M12" s="29" t="n"/>
-      <c r="N12" s="29" t="n"/>
-      <c r="O12" s="29" t="n"/>
-      <c r="P12" s="29" t="n"/>
-      <c r="Q12" s="29" t="n"/>
-      <c r="R12" s="29" t="n"/>
-      <c r="S12" s="29" t="n"/>
-      <c r="T12" s="29" t="n"/>
-      <c r="U12" s="29" t="n"/>
-      <c r="V12" s="29" t="n"/>
-      <c r="W12" s="29" t="n"/>
-      <c r="X12" s="29" t="n"/>
-      <c r="Y12" s="29" t="n"/>
-      <c r="Z12" s="29" t="n"/>
-      <c r="AA12" s="29" t="n"/>
-      <c r="AB12" s="29" t="n"/>
-      <c r="AC12" s="29" t="n"/>
-      <c r="AD12" s="29" t="n"/>
-      <c r="AE12" s="29" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF12" s="29" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG12" s="29" t="n"/>
+      <c r="C12" s="29" t="inlineStr"/>
+      <c r="D12" s="29" t="inlineStr"/>
+      <c r="E12" s="29" t="inlineStr"/>
+      <c r="F12" s="29" t="inlineStr"/>
+      <c r="G12" s="29" t="inlineStr"/>
+      <c r="H12" s="29" t="inlineStr"/>
+      <c r="I12" s="29" t="inlineStr"/>
+      <c r="J12" s="29" t="inlineStr"/>
+      <c r="K12" s="29" t="inlineStr"/>
+      <c r="L12" s="29" t="inlineStr"/>
+      <c r="M12" s="29" t="inlineStr"/>
+      <c r="N12" s="29" t="inlineStr"/>
+      <c r="O12" s="29" t="inlineStr"/>
+      <c r="P12" s="29" t="inlineStr"/>
+      <c r="Q12" s="29" t="inlineStr"/>
+      <c r="R12" s="29" t="inlineStr"/>
+      <c r="S12" s="29" t="inlineStr"/>
+      <c r="T12" s="29" t="inlineStr"/>
+      <c r="U12" s="29" t="inlineStr"/>
+      <c r="V12" s="29" t="inlineStr"/>
+      <c r="W12" s="29" t="inlineStr"/>
+      <c r="X12" s="29" t="inlineStr"/>
+      <c r="Y12" s="29" t="inlineStr"/>
+      <c r="Z12" s="29" t="inlineStr"/>
+      <c r="AA12" s="29" t="inlineStr"/>
+      <c r="AB12" s="29" t="inlineStr"/>
+      <c r="AC12" s="29" t="inlineStr"/>
+      <c r="AD12" s="29" t="inlineStr"/>
+      <c r="AE12" s="29" t="inlineStr"/>
+      <c r="AF12" s="29" t="inlineStr"/>
+      <c r="AG12" s="29" t="inlineStr"/>
     </row>
     <row r="13" ht="15.75" customFormat="1" customHeight="1" s="10">
       <c r="A13" s="8" t="n">
@@ -2108,88 +2052,72 @@
           <t>ทำความสะดาดชุดหัวเชื่อมก่อนใช้งาน</t>
         </is>
       </c>
-      <c r="C13" s="29" t="n"/>
-      <c r="D13" s="29" t="n"/>
-      <c r="E13" s="29" t="n"/>
-      <c r="F13" s="29" t="n"/>
-      <c r="G13" s="29" t="n"/>
-      <c r="H13" s="29" t="n"/>
-      <c r="I13" s="29" t="n"/>
-      <c r="J13" s="29" t="n"/>
-      <c r="K13" s="29" t="n"/>
-      <c r="L13" s="29" t="n"/>
-      <c r="M13" s="29" t="n"/>
-      <c r="N13" s="29" t="n"/>
-      <c r="O13" s="29" t="n"/>
-      <c r="P13" s="29" t="n"/>
-      <c r="Q13" s="29" t="n"/>
-      <c r="R13" s="29" t="n"/>
-      <c r="S13" s="29" t="n"/>
-      <c r="T13" s="29" t="n"/>
-      <c r="U13" s="29" t="n"/>
-      <c r="V13" s="29" t="n"/>
-      <c r="W13" s="29" t="n"/>
-      <c r="X13" s="29" t="n"/>
-      <c r="Y13" s="29" t="n"/>
-      <c r="Z13" s="29" t="n"/>
-      <c r="AA13" s="29" t="n"/>
-      <c r="AB13" s="29" t="n"/>
-      <c r="AC13" s="29" t="n"/>
-      <c r="AD13" s="29" t="n"/>
-      <c r="AE13" s="29" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF13" s="29" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG13" s="29" t="n"/>
+      <c r="C13" s="29" t="inlineStr"/>
+      <c r="D13" s="29" t="inlineStr"/>
+      <c r="E13" s="29" t="inlineStr"/>
+      <c r="F13" s="29" t="inlineStr"/>
+      <c r="G13" s="29" t="inlineStr"/>
+      <c r="H13" s="29" t="inlineStr"/>
+      <c r="I13" s="29" t="inlineStr"/>
+      <c r="J13" s="29" t="inlineStr"/>
+      <c r="K13" s="29" t="inlineStr"/>
+      <c r="L13" s="29" t="inlineStr"/>
+      <c r="M13" s="29" t="inlineStr"/>
+      <c r="N13" s="29" t="inlineStr"/>
+      <c r="O13" s="29" t="inlineStr"/>
+      <c r="P13" s="29" t="inlineStr"/>
+      <c r="Q13" s="29" t="inlineStr"/>
+      <c r="R13" s="29" t="inlineStr"/>
+      <c r="S13" s="29" t="inlineStr"/>
+      <c r="T13" s="29" t="inlineStr"/>
+      <c r="U13" s="29" t="inlineStr"/>
+      <c r="V13" s="29" t="inlineStr"/>
+      <c r="W13" s="29" t="inlineStr"/>
+      <c r="X13" s="29" t="inlineStr"/>
+      <c r="Y13" s="29" t="inlineStr"/>
+      <c r="Z13" s="29" t="inlineStr"/>
+      <c r="AA13" s="29" t="inlineStr"/>
+      <c r="AB13" s="29" t="inlineStr"/>
+      <c r="AC13" s="29" t="inlineStr"/>
+      <c r="AD13" s="29" t="inlineStr"/>
+      <c r="AE13" s="29" t="inlineStr"/>
+      <c r="AF13" s="29" t="inlineStr"/>
+      <c r="AG13" s="29" t="inlineStr"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="7" t="n"/>
       <c r="B14" s="6" t="n"/>
-      <c r="C14" s="40" t="n"/>
-      <c r="D14" s="40" t="n"/>
-      <c r="E14" s="40" t="n"/>
-      <c r="F14" s="40" t="n"/>
-      <c r="G14" s="40" t="n"/>
-      <c r="H14" s="40" t="n"/>
-      <c r="I14" s="40" t="n"/>
-      <c r="J14" s="40" t="n"/>
-      <c r="K14" s="40" t="n"/>
-      <c r="L14" s="40" t="n"/>
-      <c r="M14" s="40" t="n"/>
-      <c r="N14" s="40" t="n"/>
-      <c r="O14" s="40" t="n"/>
-      <c r="P14" s="40" t="n"/>
-      <c r="Q14" s="40" t="n"/>
-      <c r="R14" s="40" t="n"/>
-      <c r="S14" s="40" t="n"/>
-      <c r="T14" s="40" t="n"/>
-      <c r="U14" s="40" t="n"/>
-      <c r="V14" s="40" t="n"/>
-      <c r="W14" s="40" t="n"/>
-      <c r="X14" s="40" t="n"/>
-      <c r="Y14" s="40" t="n"/>
-      <c r="Z14" s="40" t="n"/>
-      <c r="AA14" s="40" t="n"/>
-      <c r="AB14" s="40" t="n"/>
-      <c r="AC14" s="40" t="n"/>
-      <c r="AD14" s="40" t="n"/>
-      <c r="AE14" s="42" t="inlineStr">
-        <is>
-          <t>อินทัช เป็นสุข</t>
-        </is>
-      </c>
-      <c r="AF14" s="42" t="inlineStr">
-        <is>
-          <t>อินทัช เป็นสุข</t>
-        </is>
-      </c>
-      <c r="AG14" s="40" t="n"/>
+      <c r="C14" s="40" t="inlineStr"/>
+      <c r="D14" s="40" t="inlineStr"/>
+      <c r="E14" s="40" t="inlineStr"/>
+      <c r="F14" s="40" t="inlineStr"/>
+      <c r="G14" s="40" t="inlineStr"/>
+      <c r="H14" s="40" t="inlineStr"/>
+      <c r="I14" s="40" t="inlineStr"/>
+      <c r="J14" s="40" t="inlineStr"/>
+      <c r="K14" s="40" t="inlineStr"/>
+      <c r="L14" s="40" t="inlineStr"/>
+      <c r="M14" s="40" t="inlineStr"/>
+      <c r="N14" s="40" t="inlineStr"/>
+      <c r="O14" s="40" t="inlineStr"/>
+      <c r="P14" s="40" t="inlineStr"/>
+      <c r="Q14" s="40" t="inlineStr"/>
+      <c r="R14" s="40" t="inlineStr"/>
+      <c r="S14" s="40" t="inlineStr"/>
+      <c r="T14" s="40" t="inlineStr"/>
+      <c r="U14" s="40" t="inlineStr"/>
+      <c r="V14" s="40" t="inlineStr"/>
+      <c r="W14" s="40" t="inlineStr"/>
+      <c r="X14" s="40" t="inlineStr"/>
+      <c r="Y14" s="40" t="inlineStr"/>
+      <c r="Z14" s="40" t="inlineStr"/>
+      <c r="AA14" s="40" t="inlineStr"/>
+      <c r="AB14" s="40" t="inlineStr"/>
+      <c r="AC14" s="40" t="inlineStr"/>
+      <c r="AD14" s="40" t="inlineStr"/>
+      <c r="AE14" s="42" t="inlineStr"/>
+      <c r="AF14" s="42" t="inlineStr"/>
+      <c r="AG14" s="40" t="inlineStr"/>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="B15" s="5" t="n"/>
@@ -2227,37 +2155,37 @@
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="B16" s="5" t="n"/>
-      <c r="C16" s="24" t="n"/>
-      <c r="D16" s="24" t="n"/>
-      <c r="E16" s="24" t="n"/>
-      <c r="F16" s="24" t="n"/>
-      <c r="G16" s="24" t="n"/>
-      <c r="H16" s="24" t="n"/>
-      <c r="I16" s="24" t="n"/>
-      <c r="J16" s="24" t="n"/>
-      <c r="K16" s="24" t="n"/>
-      <c r="L16" s="24" t="n"/>
-      <c r="M16" s="24" t="n"/>
-      <c r="N16" s="24" t="n"/>
-      <c r="O16" s="24" t="n"/>
-      <c r="P16" s="24" t="n"/>
-      <c r="Q16" s="24" t="n"/>
-      <c r="R16" s="24" t="n"/>
-      <c r="S16" s="24" t="n"/>
-      <c r="T16" s="24" t="n"/>
-      <c r="U16" s="24" t="n"/>
-      <c r="V16" s="24" t="n"/>
-      <c r="W16" s="24" t="n"/>
-      <c r="X16" s="24" t="n"/>
-      <c r="Y16" s="24" t="n"/>
-      <c r="Z16" s="24" t="n"/>
-      <c r="AA16" s="24" t="n"/>
-      <c r="AB16" s="24" t="n"/>
-      <c r="AC16" s="24" t="n"/>
-      <c r="AD16" s="24" t="n"/>
-      <c r="AE16" s="24" t="n"/>
-      <c r="AF16" s="24" t="n"/>
-      <c r="AG16" s="24" t="n"/>
+      <c r="C16" s="24" t="inlineStr"/>
+      <c r="D16" s="24" t="inlineStr"/>
+      <c r="E16" s="24" t="inlineStr"/>
+      <c r="F16" s="24" t="inlineStr"/>
+      <c r="G16" s="24" t="inlineStr"/>
+      <c r="H16" s="24" t="inlineStr"/>
+      <c r="I16" s="24" t="inlineStr"/>
+      <c r="J16" s="24" t="inlineStr"/>
+      <c r="K16" s="24" t="inlineStr"/>
+      <c r="L16" s="24" t="inlineStr"/>
+      <c r="M16" s="24" t="inlineStr"/>
+      <c r="N16" s="24" t="inlineStr"/>
+      <c r="O16" s="24" t="inlineStr"/>
+      <c r="P16" s="24" t="inlineStr"/>
+      <c r="Q16" s="24" t="inlineStr"/>
+      <c r="R16" s="24" t="inlineStr"/>
+      <c r="S16" s="24" t="inlineStr"/>
+      <c r="T16" s="24" t="inlineStr"/>
+      <c r="U16" s="24" t="inlineStr"/>
+      <c r="V16" s="24" t="inlineStr"/>
+      <c r="W16" s="24" t="inlineStr"/>
+      <c r="X16" s="24" t="inlineStr"/>
+      <c r="Y16" s="24" t="inlineStr"/>
+      <c r="Z16" s="24" t="inlineStr"/>
+      <c r="AA16" s="24" t="inlineStr"/>
+      <c r="AB16" s="24" t="inlineStr"/>
+      <c r="AC16" s="24" t="inlineStr"/>
+      <c r="AD16" s="24" t="inlineStr"/>
+      <c r="AE16" s="24" t="inlineStr"/>
+      <c r="AF16" s="24" t="inlineStr"/>
+      <c r="AG16" s="24" t="inlineStr"/>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="B17" s="5" t="n"/>

--- a/FM-MN-07_ARGON-01.xlsx
+++ b/FM-MN-07_ARGON-01.xlsx
@@ -1770,7 +1770,11 @@
       <c r="E6" s="29" t="inlineStr"/>
       <c r="F6" s="29" t="inlineStr"/>
       <c r="G6" s="29" t="inlineStr"/>
-      <c r="H6" s="29" t="inlineStr"/>
+      <c r="H6" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I6" s="29" t="inlineStr"/>
       <c r="J6" s="29" t="inlineStr"/>
       <c r="K6" s="29" t="inlineStr"/>
@@ -1811,7 +1815,11 @@
       <c r="E7" s="29" t="inlineStr"/>
       <c r="F7" s="29" t="inlineStr"/>
       <c r="G7" s="29" t="inlineStr"/>
-      <c r="H7" s="29" t="inlineStr"/>
+      <c r="H7" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I7" s="29" t="inlineStr"/>
       <c r="J7" s="29" t="inlineStr"/>
       <c r="K7" s="29" t="inlineStr"/>
@@ -1852,7 +1860,11 @@
       <c r="E8" s="29" t="inlineStr"/>
       <c r="F8" s="29" t="inlineStr"/>
       <c r="G8" s="29" t="inlineStr"/>
-      <c r="H8" s="29" t="inlineStr"/>
+      <c r="H8" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I8" s="29" t="inlineStr"/>
       <c r="J8" s="29" t="inlineStr"/>
       <c r="K8" s="29" t="inlineStr"/>
@@ -1893,7 +1905,11 @@
       <c r="E9" s="29" t="inlineStr"/>
       <c r="F9" s="29" t="inlineStr"/>
       <c r="G9" s="29" t="inlineStr"/>
-      <c r="H9" s="29" t="inlineStr"/>
+      <c r="H9" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I9" s="29" t="inlineStr"/>
       <c r="J9" s="29" t="inlineStr"/>
       <c r="K9" s="29" t="inlineStr"/>
@@ -1934,7 +1950,11 @@
       <c r="E10" s="29" t="inlineStr"/>
       <c r="F10" s="29" t="inlineStr"/>
       <c r="G10" s="29" t="inlineStr"/>
-      <c r="H10" s="29" t="inlineStr"/>
+      <c r="H10" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I10" s="29" t="inlineStr"/>
       <c r="J10" s="29" t="inlineStr"/>
       <c r="K10" s="29" t="inlineStr"/>
@@ -1975,7 +1995,11 @@
       <c r="E11" s="29" t="inlineStr"/>
       <c r="F11" s="29" t="inlineStr"/>
       <c r="G11" s="29" t="inlineStr"/>
-      <c r="H11" s="29" t="inlineStr"/>
+      <c r="H11" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I11" s="29" t="inlineStr"/>
       <c r="J11" s="29" t="inlineStr"/>
       <c r="K11" s="29" t="inlineStr"/>
@@ -2016,7 +2040,11 @@
       <c r="E12" s="29" t="inlineStr"/>
       <c r="F12" s="29" t="inlineStr"/>
       <c r="G12" s="29" t="inlineStr"/>
-      <c r="H12" s="29" t="inlineStr"/>
+      <c r="H12" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I12" s="29" t="inlineStr"/>
       <c r="J12" s="29" t="inlineStr"/>
       <c r="K12" s="29" t="inlineStr"/>
@@ -2057,7 +2085,11 @@
       <c r="E13" s="29" t="inlineStr"/>
       <c r="F13" s="29" t="inlineStr"/>
       <c r="G13" s="29" t="inlineStr"/>
-      <c r="H13" s="29" t="inlineStr"/>
+      <c r="H13" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I13" s="29" t="inlineStr"/>
       <c r="J13" s="29" t="inlineStr"/>
       <c r="K13" s="29" t="inlineStr"/>
@@ -2092,7 +2124,11 @@
       <c r="E14" s="40" t="inlineStr"/>
       <c r="F14" s="40" t="inlineStr"/>
       <c r="G14" s="40" t="inlineStr"/>
-      <c r="H14" s="40" t="inlineStr"/>
+      <c r="H14" s="42" t="inlineStr">
+        <is>
+          <t>อินทัช เป็นสุข</t>
+        </is>
+      </c>
       <c r="I14" s="40" t="inlineStr"/>
       <c r="J14" s="40" t="inlineStr"/>
       <c r="K14" s="40" t="inlineStr"/>

--- a/FM-MN-07_ARGON-01.xlsx
+++ b/FM-MN-07_ARGON-01.xlsx
@@ -1775,7 +1775,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I6" s="29" t="inlineStr"/>
+      <c r="I6" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J6" s="29" t="inlineStr"/>
       <c r="K6" s="29" t="inlineStr"/>
       <c r="L6" s="29" t="inlineStr"/>
@@ -1820,7 +1824,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I7" s="29" t="inlineStr"/>
+      <c r="I7" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J7" s="29" t="inlineStr"/>
       <c r="K7" s="29" t="inlineStr"/>
       <c r="L7" s="29" t="inlineStr"/>
@@ -1865,7 +1873,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I8" s="29" t="inlineStr"/>
+      <c r="I8" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J8" s="29" t="inlineStr"/>
       <c r="K8" s="29" t="inlineStr"/>
       <c r="L8" s="29" t="inlineStr"/>
@@ -1910,7 +1922,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I9" s="29" t="inlineStr"/>
+      <c r="I9" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J9" s="29" t="inlineStr"/>
       <c r="K9" s="29" t="inlineStr"/>
       <c r="L9" s="29" t="inlineStr"/>
@@ -1955,7 +1971,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I10" s="29" t="inlineStr"/>
+      <c r="I10" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J10" s="29" t="inlineStr"/>
       <c r="K10" s="29" t="inlineStr"/>
       <c r="L10" s="29" t="inlineStr"/>
@@ -2000,7 +2020,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I11" s="29" t="inlineStr"/>
+      <c r="I11" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J11" s="29" t="inlineStr"/>
       <c r="K11" s="29" t="inlineStr"/>
       <c r="L11" s="29" t="inlineStr"/>
@@ -2045,7 +2069,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I12" s="29" t="inlineStr"/>
+      <c r="I12" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J12" s="29" t="inlineStr"/>
       <c r="K12" s="29" t="inlineStr"/>
       <c r="L12" s="29" t="inlineStr"/>
@@ -2090,7 +2118,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I13" s="29" t="inlineStr"/>
+      <c r="I13" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J13" s="29" t="inlineStr"/>
       <c r="K13" s="29" t="inlineStr"/>
       <c r="L13" s="29" t="inlineStr"/>
@@ -2129,7 +2161,11 @@
           <t>อินทัช เป็นสุข</t>
         </is>
       </c>
-      <c r="I14" s="40" t="inlineStr"/>
+      <c r="I14" s="42" t="inlineStr">
+        <is>
+          <t>อินทัช เป็นสุข</t>
+        </is>
+      </c>
       <c r="J14" s="40" t="inlineStr"/>
       <c r="K14" s="40" t="inlineStr"/>
       <c r="L14" s="40" t="inlineStr"/>

--- a/FM-MN-07_ARGON-01.xlsx
+++ b/FM-MN-07_ARGON-01.xlsx
@@ -1780,7 +1780,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J6" s="29" t="inlineStr"/>
+      <c r="J6" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K6" s="29" t="inlineStr"/>
       <c r="L6" s="29" t="inlineStr"/>
       <c r="M6" s="29" t="inlineStr"/>
@@ -1829,7 +1833,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J7" s="29" t="inlineStr"/>
+      <c r="J7" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K7" s="29" t="inlineStr"/>
       <c r="L7" s="29" t="inlineStr"/>
       <c r="M7" s="29" t="inlineStr"/>
@@ -1878,7 +1886,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J8" s="29" t="inlineStr"/>
+      <c r="J8" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K8" s="29" t="inlineStr"/>
       <c r="L8" s="29" t="inlineStr"/>
       <c r="M8" s="29" t="inlineStr"/>
@@ -1927,7 +1939,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J9" s="29" t="inlineStr"/>
+      <c r="J9" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K9" s="29" t="inlineStr"/>
       <c r="L9" s="29" t="inlineStr"/>
       <c r="M9" s="29" t="inlineStr"/>
@@ -1976,7 +1992,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J10" s="29" t="inlineStr"/>
+      <c r="J10" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K10" s="29" t="inlineStr"/>
       <c r="L10" s="29" t="inlineStr"/>
       <c r="M10" s="29" t="inlineStr"/>
@@ -2025,7 +2045,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J11" s="29" t="inlineStr"/>
+      <c r="J11" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K11" s="29" t="inlineStr"/>
       <c r="L11" s="29" t="inlineStr"/>
       <c r="M11" s="29" t="inlineStr"/>
@@ -2074,7 +2098,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J12" s="29" t="inlineStr"/>
+      <c r="J12" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K12" s="29" t="inlineStr"/>
       <c r="L12" s="29" t="inlineStr"/>
       <c r="M12" s="29" t="inlineStr"/>
@@ -2123,7 +2151,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J13" s="29" t="inlineStr"/>
+      <c r="J13" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K13" s="29" t="inlineStr"/>
       <c r="L13" s="29" t="inlineStr"/>
       <c r="M13" s="29" t="inlineStr"/>
@@ -2166,7 +2198,11 @@
           <t>อินทัช เป็นสุข</t>
         </is>
       </c>
-      <c r="J14" s="40" t="inlineStr"/>
+      <c r="J14" s="42" t="inlineStr">
+        <is>
+          <t>อินทัช เป็นสุข</t>
+        </is>
+      </c>
       <c r="K14" s="40" t="inlineStr"/>
       <c r="L14" s="40" t="inlineStr"/>
       <c r="M14" s="40" t="inlineStr"/>

--- a/FM-MN-07_ARGON-01.xlsx
+++ b/FM-MN-07_ARGON-01.xlsx
@@ -1786,7 +1786,11 @@
         </is>
       </c>
       <c r="K6" s="29" t="inlineStr"/>
-      <c r="L6" s="29" t="inlineStr"/>
+      <c r="L6" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M6" s="29" t="inlineStr"/>
       <c r="N6" s="29" t="inlineStr"/>
       <c r="O6" s="29" t="inlineStr"/>
@@ -1839,7 +1843,11 @@
         </is>
       </c>
       <c r="K7" s="29" t="inlineStr"/>
-      <c r="L7" s="29" t="inlineStr"/>
+      <c r="L7" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M7" s="29" t="inlineStr"/>
       <c r="N7" s="29" t="inlineStr"/>
       <c r="O7" s="29" t="inlineStr"/>
@@ -1892,7 +1900,11 @@
         </is>
       </c>
       <c r="K8" s="29" t="inlineStr"/>
-      <c r="L8" s="29" t="inlineStr"/>
+      <c r="L8" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M8" s="29" t="inlineStr"/>
       <c r="N8" s="29" t="inlineStr"/>
       <c r="O8" s="29" t="inlineStr"/>
@@ -1945,7 +1957,11 @@
         </is>
       </c>
       <c r="K9" s="29" t="inlineStr"/>
-      <c r="L9" s="29" t="inlineStr"/>
+      <c r="L9" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M9" s="29" t="inlineStr"/>
       <c r="N9" s="29" t="inlineStr"/>
       <c r="O9" s="29" t="inlineStr"/>
@@ -1998,7 +2014,11 @@
         </is>
       </c>
       <c r="K10" s="29" t="inlineStr"/>
-      <c r="L10" s="29" t="inlineStr"/>
+      <c r="L10" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M10" s="29" t="inlineStr"/>
       <c r="N10" s="29" t="inlineStr"/>
       <c r="O10" s="29" t="inlineStr"/>
@@ -2051,7 +2071,11 @@
         </is>
       </c>
       <c r="K11" s="29" t="inlineStr"/>
-      <c r="L11" s="29" t="inlineStr"/>
+      <c r="L11" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M11" s="29" t="inlineStr"/>
       <c r="N11" s="29" t="inlineStr"/>
       <c r="O11" s="29" t="inlineStr"/>
@@ -2104,7 +2128,11 @@
         </is>
       </c>
       <c r="K12" s="29" t="inlineStr"/>
-      <c r="L12" s="29" t="inlineStr"/>
+      <c r="L12" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M12" s="29" t="inlineStr"/>
       <c r="N12" s="29" t="inlineStr"/>
       <c r="O12" s="29" t="inlineStr"/>
@@ -2157,7 +2185,11 @@
         </is>
       </c>
       <c r="K13" s="29" t="inlineStr"/>
-      <c r="L13" s="29" t="inlineStr"/>
+      <c r="L13" s="29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M13" s="29" t="inlineStr"/>
       <c r="N13" s="29" t="inlineStr"/>
       <c r="O13" s="29" t="inlineStr"/>
@@ -2204,7 +2236,11 @@
         </is>
       </c>
       <c r="K14" s="40" t="inlineStr"/>
-      <c r="L14" s="40" t="inlineStr"/>
+      <c r="L14" s="42" t="inlineStr">
+        <is>
+          <t>คะนอง บัวจันทร์</t>
+        </is>
+      </c>
       <c r="M14" s="40" t="inlineStr"/>
       <c r="N14" s="40" t="inlineStr"/>
       <c r="O14" s="40" t="inlineStr"/>
